--- a/public/template_excel/FRM-MR-M3-017-02 SUMMARY AUDIT INTERNAL.xlsx
+++ b/public/template_excel/FRM-MR-M3-017-02 SUMMARY AUDIT INTERNAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sanya\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sanya\Madonna\donnav2\public\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3666E790-3B20-4698-91E8-79C97844FE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13671B5-5724-46FF-8596-E413FF1C6E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary Audit (ALL)" sheetId="1" r:id="rId1"/>
@@ -308,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -321,9 +321,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -347,23 +344,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -377,17 +368,29 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -672,162 +675,163 @@
   <dimension ref="B2:Q82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="10" customWidth="1"/>
-    <col min="4" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="107.85546875" style="11" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="12" customWidth="1"/>
-    <col min="10" max="11" width="13.85546875" style="12" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="12" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="107.85546875" style="10" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="11" customWidth="1"/>
+    <col min="10" max="11" width="13.85546875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="11" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
     </row>
     <row r="3" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
     </row>
     <row r="4" spans="2:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="2:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="19"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="2:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="21"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="1" t="s">
         <v>10</v>
       </c>
@@ -859,8 +863,8 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -880,7 +884,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -900,7 +904,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -919,8 +923,8 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -940,7 +944,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -960,7 +964,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -980,7 +984,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1000,7 +1004,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1018,9 +1022,9 @@
         <v>9</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1038,9 +1042,9 @@
         <v>10</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1058,9 +1062,9 @@
         <v>11</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1078,9 +1082,9 @@
         <v>12</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1098,9 +1102,9 @@
         <v>13</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1118,9 +1122,9 @@
         <v>14</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="6"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -1140,7 +1144,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1160,7 +1164,7 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1180,7 +1184,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1200,16 +1204,16 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
@@ -1220,16 +1224,16 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
@@ -1240,16 +1244,16 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
@@ -1260,16 +1264,16 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
@@ -1280,16 +1284,16 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
@@ -1300,16 +1304,16 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
@@ -1320,16 +1324,16 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
@@ -1340,16 +1344,16 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
@@ -1360,16 +1364,16 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
@@ -1380,16 +1384,16 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
@@ -1400,16 +1404,16 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
@@ -1420,7 +1424,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="6"/>
+      <c r="F37" s="5"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -1438,18 +1442,18 @@
         <v>30</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="6"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
@@ -1458,9 +1462,9 @@
         <v>31</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="7"/>
+      <c r="D39" s="6"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="6"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -1478,9 +1482,9 @@
         <v>32</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -1490,8 +1494,8 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
@@ -1500,7 +1504,7 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="6"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -1518,9 +1522,9 @@
         <v>34</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -1530,8 +1534,8 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
@@ -1540,7 +1544,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="6"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -1558,9 +1562,9 @@
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -1570,8 +1574,8 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
@@ -1580,7 +1584,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="6"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -1598,9 +1602,9 @@
         <v>38</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -1610,8 +1614,8 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
@@ -1620,7 +1624,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -1638,9 +1642,9 @@
         <v>40</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -1650,8 +1654,8 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
@@ -1660,7 +1664,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="6"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -1678,9 +1682,9 @@
         <v>42</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -1690,8 +1694,8 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
@@ -1700,7 +1704,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="6"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -1718,9 +1722,9 @@
         <v>44</v>
       </c>
       <c r="C52" s="4"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -1730,8 +1734,8 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
@@ -1740,7 +1744,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -1758,9 +1762,9 @@
         <v>46</v>
       </c>
       <c r="C54" s="4"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="8"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -1770,8 +1774,8 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
     </row>
     <row r="55" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
@@ -1780,7 +1784,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -1798,9 +1802,9 @@
         <v>48</v>
       </c>
       <c r="C56" s="4"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -1810,8 +1814,8 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
     </row>
     <row r="57" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
@@ -1820,7 +1824,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="6"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -1838,9 +1842,9 @@
         <v>50</v>
       </c>
       <c r="C58" s="4"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -1850,8 +1854,8 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
@@ -1860,7 +1864,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="6"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -1878,9 +1882,9 @@
         <v>52</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -1890,8 +1894,8 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
     </row>
     <row r="61" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
@@ -1900,7 +1904,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="6"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -1918,9 +1922,9 @@
         <v>54</v>
       </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -1930,8 +1934,8 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="8"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
     </row>
     <row r="63" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
@@ -1940,7 +1944,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="6"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -1958,9 +1962,9 @@
         <v>56</v>
       </c>
       <c r="C64" s="4"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -1970,8 +1974,8 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
     </row>
     <row r="65" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
@@ -1980,7 +1984,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -1998,9 +2002,9 @@
         <v>58</v>
       </c>
       <c r="C66" s="4"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -2010,8 +2014,8 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="8"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
     </row>
     <row r="67" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
@@ -2020,7 +2024,7 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
+      <c r="F67" s="5"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -2038,9 +2042,9 @@
         <v>60</v>
       </c>
       <c r="C68" s="4"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -2050,8 +2054,8 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
     </row>
     <row r="69" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
@@ -2060,7 +2064,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="6"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -2078,9 +2082,9 @@
         <v>62</v>
       </c>
       <c r="C70" s="4"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -2090,8 +2094,8 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="8"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
     </row>
     <row r="71" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
@@ -2100,7 +2104,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -2118,9 +2122,9 @@
         <v>64</v>
       </c>
       <c r="C72" s="4"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -2130,8 +2134,8 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="4">
@@ -2140,7 +2144,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -2158,9 +2162,9 @@
         <v>66</v>
       </c>
       <c r="C74" s="4"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -2170,8 +2174,8 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
@@ -2180,7 +2184,7 @@
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="5"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -2198,9 +2202,9 @@
         <v>68</v>
       </c>
       <c r="C76" s="4"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -2210,8 +2214,8 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="4">
@@ -2220,7 +2224,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -2240,7 +2244,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -2260,7 +2264,7 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -2280,7 +2284,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -2294,26 +2298,26 @@
       <c r="Q80" s="4"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B3:Q3"/>
     <mergeCell ref="B4:Q4"/>
     <mergeCell ref="B5:Q5"/>
     <mergeCell ref="B6:Q6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2326,164 +2330,165 @@
   <dimension ref="B2:Q82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="10" customWidth="1"/>
-    <col min="4" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="107.85546875" style="11" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="12" customWidth="1"/>
-    <col min="10" max="11" width="13.85546875" style="12" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="12" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="107.85546875" style="10" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="11" customWidth="1"/>
+    <col min="10" max="11" width="13.85546875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="11" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
     </row>
     <row r="3" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
     </row>
     <row r="4" spans="2:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="2:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="19"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="2:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="21"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="1" t="s">
         <v>10</v>
       </c>
@@ -2515,8 +2520,8 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -2536,7 +2541,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -2556,7 +2561,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -2575,8 +2580,8 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -2596,7 +2601,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -2616,7 +2621,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -2636,7 +2641,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -2656,7 +2661,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -2674,9 +2679,9 @@
         <v>9</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -2694,9 +2699,9 @@
         <v>10</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -2714,9 +2719,9 @@
         <v>11</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -2734,9 +2739,9 @@
         <v>12</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -2754,9 +2759,9 @@
         <v>13</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -2774,9 +2779,9 @@
         <v>14</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="6"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -2796,7 +2801,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -2816,7 +2821,7 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -2836,7 +2841,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -2856,16 +2861,16 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
@@ -2876,16 +2881,16 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
@@ -2896,16 +2901,16 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
@@ -2916,16 +2921,16 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
@@ -2936,16 +2941,16 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
@@ -2956,16 +2961,16 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
@@ -2976,16 +2981,16 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
@@ -2996,16 +3001,16 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
@@ -3016,16 +3021,16 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
@@ -3036,16 +3041,16 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
@@ -3056,16 +3061,16 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
@@ -3076,7 +3081,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="6"/>
+      <c r="F37" s="5"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -3094,18 +3099,18 @@
         <v>30</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="6"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
@@ -3114,9 +3119,9 @@
         <v>31</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="7"/>
+      <c r="D39" s="6"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="6"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -3134,9 +3139,9 @@
         <v>32</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -3146,8 +3151,8 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
@@ -3156,7 +3161,7 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="6"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -3174,9 +3179,9 @@
         <v>34</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -3186,8 +3191,8 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
@@ -3196,7 +3201,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="6"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -3214,9 +3219,9 @@
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -3226,8 +3231,8 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
@@ -3236,7 +3241,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="6"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -3254,9 +3259,9 @@
         <v>38</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -3266,8 +3271,8 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
@@ -3276,7 +3281,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -3294,9 +3299,9 @@
         <v>40</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -3306,8 +3311,8 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
@@ -3316,7 +3321,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="6"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -3334,9 +3339,9 @@
         <v>42</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -3346,8 +3351,8 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
@@ -3356,7 +3361,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="6"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -3374,9 +3379,9 @@
         <v>44</v>
       </c>
       <c r="C52" s="4"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -3386,8 +3391,8 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
@@ -3396,7 +3401,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -3414,9 +3419,9 @@
         <v>46</v>
       </c>
       <c r="C54" s="4"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="8"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -3426,8 +3431,8 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
     </row>
     <row r="55" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
@@ -3436,7 +3441,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -3454,9 +3459,9 @@
         <v>48</v>
       </c>
       <c r="C56" s="4"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -3466,8 +3471,8 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
     </row>
     <row r="57" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
@@ -3476,7 +3481,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="6"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -3494,9 +3499,9 @@
         <v>50</v>
       </c>
       <c r="C58" s="4"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -3506,8 +3511,8 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
@@ -3516,7 +3521,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="6"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -3534,9 +3539,9 @@
         <v>52</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -3546,8 +3551,8 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
     </row>
     <row r="61" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
@@ -3556,7 +3561,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="6"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -3574,9 +3579,9 @@
         <v>54</v>
       </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -3586,8 +3591,8 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="8"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
     </row>
     <row r="63" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
@@ -3596,7 +3601,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="6"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -3614,9 +3619,9 @@
         <v>56</v>
       </c>
       <c r="C64" s="4"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -3626,8 +3631,8 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
     </row>
     <row r="65" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
@@ -3636,7 +3641,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -3654,9 +3659,9 @@
         <v>58</v>
       </c>
       <c r="C66" s="4"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -3666,8 +3671,8 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="8"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
     </row>
     <row r="67" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
@@ -3676,7 +3681,7 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
+      <c r="F67" s="5"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -3694,9 +3699,9 @@
         <v>60</v>
       </c>
       <c r="C68" s="4"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -3706,8 +3711,8 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
     </row>
     <row r="69" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
@@ -3716,7 +3721,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="6"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -3734,9 +3739,9 @@
         <v>62</v>
       </c>
       <c r="C70" s="4"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -3746,8 +3751,8 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="8"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
     </row>
     <row r="71" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
@@ -3756,7 +3761,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -3774,9 +3779,9 @@
         <v>64</v>
       </c>
       <c r="C72" s="4"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -3786,8 +3791,8 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="4">
@@ -3796,7 +3801,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -3814,9 +3819,9 @@
         <v>66</v>
       </c>
       <c r="C74" s="4"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -3826,8 +3831,8 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
@@ -3836,7 +3841,7 @@
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="5"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -3854,9 +3859,9 @@
         <v>68</v>
       </c>
       <c r="C76" s="4"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -3866,8 +3871,8 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="4">
@@ -3876,7 +3881,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -3896,7 +3901,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -3916,7 +3921,7 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -3936,7 +3941,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -3950,26 +3955,26 @@
       <c r="Q80" s="4"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
+    <mergeCell ref="B6:Q6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
-    <mergeCell ref="B6:Q6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3982,164 +3987,165 @@
   <dimension ref="B2:Q82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="10" customWidth="1"/>
-    <col min="4" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="107.85546875" style="11" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="12" customWidth="1"/>
-    <col min="10" max="11" width="13.85546875" style="12" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="12" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="107.85546875" style="10" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="11" customWidth="1"/>
+    <col min="10" max="11" width="13.85546875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="11" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
     </row>
     <row r="3" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
     </row>
     <row r="4" spans="2:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="2:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="19"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="2:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="21"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="1" t="s">
         <v>10</v>
       </c>
@@ -4171,8 +4177,8 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -4192,7 +4198,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -4212,7 +4218,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -4231,8 +4237,8 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -4252,7 +4258,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -4272,7 +4278,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -4292,7 +4298,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -4312,7 +4318,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -4330,9 +4336,9 @@
         <v>9</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -4350,9 +4356,9 @@
         <v>10</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -4370,9 +4376,9 @@
         <v>11</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -4390,9 +4396,9 @@
         <v>12</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -4410,9 +4416,9 @@
         <v>13</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -4430,9 +4436,9 @@
         <v>14</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="6"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -4452,7 +4458,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -4472,7 +4478,7 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -4492,7 +4498,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -4512,16 +4518,16 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
@@ -4532,16 +4538,16 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
@@ -4552,16 +4558,16 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
@@ -4572,16 +4578,16 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
@@ -4592,16 +4598,16 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
@@ -4612,16 +4618,16 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
@@ -4632,16 +4638,16 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
@@ -4652,16 +4658,16 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
@@ -4672,16 +4678,16 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
@@ -4692,16 +4698,16 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
@@ -4712,16 +4718,16 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
@@ -4732,7 +4738,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="6"/>
+      <c r="F37" s="5"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -4750,18 +4756,18 @@
         <v>30</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="6"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
@@ -4770,9 +4776,9 @@
         <v>31</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="7"/>
+      <c r="D39" s="6"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="6"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -4790,9 +4796,9 @@
         <v>32</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -4802,8 +4808,8 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
@@ -4812,7 +4818,7 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="6"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -4830,9 +4836,9 @@
         <v>34</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -4842,8 +4848,8 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
@@ -4852,7 +4858,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="6"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -4870,9 +4876,9 @@
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -4882,8 +4888,8 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
@@ -4892,7 +4898,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="6"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -4910,9 +4916,9 @@
         <v>38</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -4922,8 +4928,8 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
@@ -4932,7 +4938,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -4950,9 +4956,9 @@
         <v>40</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -4962,8 +4968,8 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
@@ -4972,7 +4978,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="6"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -4990,9 +4996,9 @@
         <v>42</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -5002,8 +5008,8 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
@@ -5012,7 +5018,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="6"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -5030,9 +5036,9 @@
         <v>44</v>
       </c>
       <c r="C52" s="4"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -5042,8 +5048,8 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
@@ -5052,7 +5058,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -5070,9 +5076,9 @@
         <v>46</v>
       </c>
       <c r="C54" s="4"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="8"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -5082,8 +5088,8 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
     </row>
     <row r="55" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
@@ -5092,7 +5098,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -5110,9 +5116,9 @@
         <v>48</v>
       </c>
       <c r="C56" s="4"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -5122,8 +5128,8 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
     </row>
     <row r="57" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
@@ -5132,7 +5138,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="6"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -5150,9 +5156,9 @@
         <v>50</v>
       </c>
       <c r="C58" s="4"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -5162,8 +5168,8 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
@@ -5172,7 +5178,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="6"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -5190,9 +5196,9 @@
         <v>52</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -5202,8 +5208,8 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
     </row>
     <row r="61" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
@@ -5212,7 +5218,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="6"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -5230,9 +5236,9 @@
         <v>54</v>
       </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -5242,8 +5248,8 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="8"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
     </row>
     <row r="63" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
@@ -5252,7 +5258,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="6"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -5270,9 +5276,9 @@
         <v>56</v>
       </c>
       <c r="C64" s="4"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -5282,8 +5288,8 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
     </row>
     <row r="65" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
@@ -5292,7 +5298,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -5310,9 +5316,9 @@
         <v>58</v>
       </c>
       <c r="C66" s="4"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -5322,8 +5328,8 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="8"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
     </row>
     <row r="67" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
@@ -5332,7 +5338,7 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
+      <c r="F67" s="5"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -5350,9 +5356,9 @@
         <v>60</v>
       </c>
       <c r="C68" s="4"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -5362,8 +5368,8 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
     </row>
     <row r="69" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
@@ -5372,7 +5378,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="6"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -5390,9 +5396,9 @@
         <v>62</v>
       </c>
       <c r="C70" s="4"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -5402,8 +5408,8 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="8"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
     </row>
     <row r="71" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
@@ -5412,7 +5418,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -5430,9 +5436,9 @@
         <v>64</v>
       </c>
       <c r="C72" s="4"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -5442,8 +5448,8 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="4">
@@ -5452,7 +5458,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -5470,9 +5476,9 @@
         <v>66</v>
       </c>
       <c r="C74" s="4"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -5482,8 +5488,8 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
@@ -5492,7 +5498,7 @@
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="5"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -5510,9 +5516,9 @@
         <v>68</v>
       </c>
       <c r="C76" s="4"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -5522,8 +5528,8 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="4">
@@ -5532,7 +5538,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -5552,7 +5558,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -5572,7 +5578,7 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -5592,7 +5598,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -5606,26 +5612,26 @@
       <c r="Q80" s="4"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
+    <mergeCell ref="B6:Q6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
-    <mergeCell ref="B6:Q6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5638,164 +5644,165 @@
   <dimension ref="B2:Q82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="10" customWidth="1"/>
-    <col min="4" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="107.85546875" style="11" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="12" customWidth="1"/>
-    <col min="10" max="11" width="13.85546875" style="12" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="12" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="107.85546875" style="10" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="11" customWidth="1"/>
+    <col min="10" max="11" width="13.85546875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="11" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
     </row>
     <row r="3" spans="2:17" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
     </row>
     <row r="4" spans="2:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="2:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="19"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="2:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="21"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="1" t="s">
         <v>10</v>
       </c>
@@ -5827,8 +5834,8 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -5848,7 +5855,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -5868,7 +5875,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -5887,8 +5894,8 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -5908,7 +5915,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -5928,7 +5935,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -5948,7 +5955,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -5968,7 +5975,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -5986,9 +5993,9 @@
         <v>9</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -6006,9 +6013,9 @@
         <v>10</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -6026,9 +6033,9 @@
         <v>11</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -6046,9 +6053,9 @@
         <v>12</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -6066,9 +6073,9 @@
         <v>13</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -6086,9 +6093,9 @@
         <v>14</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="6"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -6108,7 +6115,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -6128,7 +6135,7 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -6148,7 +6155,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -6168,16 +6175,16 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
@@ -6188,16 +6195,16 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
@@ -6208,16 +6215,16 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
@@ -6228,16 +6235,16 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
@@ -6248,16 +6255,16 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
@@ -6268,16 +6275,16 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
@@ -6288,16 +6295,16 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
@@ -6308,16 +6315,16 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
@@ -6328,16 +6335,16 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
@@ -6348,16 +6355,16 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
@@ -6368,16 +6375,16 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
@@ -6388,7 +6395,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="6"/>
+      <c r="F37" s="5"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -6406,18 +6413,18 @@
         <v>30</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="6"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
@@ -6426,9 +6433,9 @@
         <v>31</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="7"/>
+      <c r="D39" s="6"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="6"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -6446,9 +6453,9 @@
         <v>32</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -6458,8 +6465,8 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
@@ -6468,7 +6475,7 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="6"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -6486,9 +6493,9 @@
         <v>34</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -6498,8 +6505,8 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
@@ -6508,7 +6515,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="6"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -6526,9 +6533,9 @@
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -6538,8 +6545,8 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
@@ -6548,7 +6555,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="6"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -6566,9 +6573,9 @@
         <v>38</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -6578,8 +6585,8 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
@@ -6588,7 +6595,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -6606,9 +6613,9 @@
         <v>40</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -6618,8 +6625,8 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
@@ -6628,7 +6635,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="6"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -6646,9 +6653,9 @@
         <v>42</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -6658,8 +6665,8 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
@@ -6668,7 +6675,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="6"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -6686,9 +6693,9 @@
         <v>44</v>
       </c>
       <c r="C52" s="4"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -6698,8 +6705,8 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
@@ -6708,7 +6715,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -6726,9 +6733,9 @@
         <v>46</v>
       </c>
       <c r="C54" s="4"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="8"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -6738,8 +6745,8 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
     </row>
     <row r="55" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
@@ -6748,7 +6755,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -6766,9 +6773,9 @@
         <v>48</v>
       </c>
       <c r="C56" s="4"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -6778,8 +6785,8 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
     </row>
     <row r="57" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
@@ -6788,7 +6795,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="6"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -6806,9 +6813,9 @@
         <v>50</v>
       </c>
       <c r="C58" s="4"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -6818,8 +6825,8 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
@@ -6828,7 +6835,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="6"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -6846,9 +6853,9 @@
         <v>52</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -6858,8 +6865,8 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
     </row>
     <row r="61" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
@@ -6868,7 +6875,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="6"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -6886,9 +6893,9 @@
         <v>54</v>
       </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -6898,8 +6905,8 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="8"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
     </row>
     <row r="63" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
@@ -6908,7 +6915,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="6"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -6926,9 +6933,9 @@
         <v>56</v>
       </c>
       <c r="C64" s="4"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -6938,8 +6945,8 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
     </row>
     <row r="65" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
@@ -6948,7 +6955,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -6966,9 +6973,9 @@
         <v>58</v>
       </c>
       <c r="C66" s="4"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -6978,8 +6985,8 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="8"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
     </row>
     <row r="67" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
@@ -6988,7 +6995,7 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
+      <c r="F67" s="5"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -7006,9 +7013,9 @@
         <v>60</v>
       </c>
       <c r="C68" s="4"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -7018,8 +7025,8 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
     </row>
     <row r="69" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
@@ -7028,7 +7035,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="6"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -7046,9 +7053,9 @@
         <v>62</v>
       </c>
       <c r="C70" s="4"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -7058,8 +7065,8 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="8"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
     </row>
     <row r="71" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
@@ -7068,7 +7075,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -7086,9 +7093,9 @@
         <v>64</v>
       </c>
       <c r="C72" s="4"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -7098,8 +7105,8 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="4">
@@ -7108,7 +7115,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -7126,9 +7133,9 @@
         <v>66</v>
       </c>
       <c r="C74" s="4"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -7138,8 +7145,8 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
@@ -7148,7 +7155,7 @@
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="5"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -7166,9 +7173,9 @@
         <v>68</v>
       </c>
       <c r="C76" s="4"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -7178,8 +7185,8 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="2:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="4">
@@ -7188,7 +7195,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -7208,7 +7215,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -7228,7 +7235,7 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -7248,7 +7255,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -7262,26 +7269,26 @@
       <c r="Q80" s="4"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
+    <mergeCell ref="B6:Q6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
-    <mergeCell ref="B6:Q6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
